--- a/data/screened/human_adjudication_blinded.xlsx
+++ b/data/screened/human_adjudication_blinded.xlsx
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Decide on the title and abstract only. If there is no abstract, use the title, venue, and document type.</t>
+          <t>Decide on the title and abstract only (plus year, venue, and document type), not the full paper. If there is no abstract, use the title, venue, and document type.</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Scope test: is the record about adoption or implementation of interoperable eHealth systems (EHR/EMR/HIE/health-IT infrastructure) at the organizational or national/system level?</t>
+          <t>Scope test: is the record about adoption or implementation of eHealth systems (EHR/EMR/HIE/health-IT infrastructure, including interoperability) at the organizational or national/system level? The level refers to the system being adopted, not to whether the respondents are individual clinicians or staff (README condition 6).</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Do not open human_adjudication_worklist.csv, two_rater_comparison.csv, or three_way_comparison.csv until you finish. They show the AI answers.</t>
+          <t>This workbook contains nothing that shows how the automated screen decided any record. Decide each record yourself, and please do not ask the author about a specific record until you have finished (README section 9).</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>To see what is left, filter your_decision for blanks. Do not delete rows or edit the other columns. Save often, under the same file name.</t>
+          <t>To see what is left, filter your_decision for blanks. Do not delete rows or edit the other columns. Save often. When you have finished, save under the same name with your initials added, for example human_adjudication_blinded_JD.xlsx (README section 10).</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Definitions: analysis/screening_rubric.md. E5 (duplicate / non-English) is left out because the screen never used it.</t>
+          <t>Definitions: screening_rubric.md (in this folder) and README section 7. E5 (duplicate / non-English) is left out because the screen never used it.</t>
         </is>
       </c>
     </row>
